--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -26,6 +26,7 @@
     <sheet name="magapoke_2026-02-11" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="magapoke_2026-02-18" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="magapoke_2026-02-25" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="magapoke_2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12749,6 +12750,1032 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ベイビーステップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ひゃくえむ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>追放されなかった男　～二度目の人生は土下座から始まりました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>デッドアカウント</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>幼馴染とはラブコメにならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>春くらり</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>追放された転生王子、『自動製作《オートクラフト》』スキルで領地を爆速で開拓し最強の村を作ってしまう〜最強クラフトスキルで始める、楽々領地開拓スローライフ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fate/Grand Order -Epic of Remnant- 英霊剣豪七番勝負</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>グラぱらっ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ハンドレッドノート－アグリーダック－</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>お母さん冒険者、ログインボーナスでスキル【主婦】に目覚めました。週一貰えるチラシで冒険者生活頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>味方が弱すぎて補助魔法に徹していた宮廷魔法師、追放されて最強を目指す</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>異世界グルメで成り上がり無双～山に追放されたので、のんびりキャンプを楽しんでいたらいつの間にか強くなっていて、王侯貴族や実力者たちが俺を放っておいてくれません。一方、俺を追放した貴族たちは破滅が始まる～</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>おやすみ ふみさん</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>なれの果ての僕ら</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>時々ボソッとロシア語でデレる隣のアーリャさん</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>アオバノバスケ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>不遇職【鑑定士】が実は最強だった～奈落で鍛えた最強の【神眼】で無双する～</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Aランクパーティを離脱した俺は、元教え子たちと迷宮深部を目指す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>普通の本はありません！</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>アルキメデスの大戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>南海トラフ巨大地震</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>最弱な僕は＜壁抜けバグ＞で成り上がる～壁をすり抜けたら、初回クリア報酬を無限回収できました！～</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Destiny Unchain Online 〜吸血鬼少女となって、やがて『赤の魔王』と呼ばれるようになりました〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ジュミドロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>さわらないで小手指くん</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>辺境の薬師、都でSランク冒険者となる～英雄村の少年がチート薬で無自覚無双〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>いじめるヤバイ奴</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ルックスＹを選んでしまいました 〜やり込んでいるゲームに転生したはずなのに、未実装のガチャで攻略をすることになった件〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ペンの夢に紅をさす</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>我間乱 ―修羅―</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>復讐の教科書</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>屋根の下のアルテミス</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>おくることば</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ～場地圭介からの手紙～</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>不遇職『鍛冶師』だけど最強です ～気づけば何でも作れるようになっていた男ののんびりスローライフ～</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>降り積もれ孤独な死よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>日本語が話せないロシア人美少女転入生が頼れるのは、多言語マスターの俺1人</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>阿武ノーマル</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>白鳥運子は31画</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>恋ニ非ズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>可愛いだけじゃない式守さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>五輪の女神さま 〜なでしこ寮のメダルごはん〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>剣帝学院の魔眼賢者</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ストーカー行為がバレて人生終了男</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>デスティニーラバーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>念願の悪役令嬢（ラスボス）の身体を手に入れたぞ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>この世界がいずれ滅ぶことを、俺だけが知っている～モンスターが現れた世界で、死に戻りレベルアップ～</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>東京ネオンスキャンダル</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>田んぼで拾った女騎士、田舎で俺の嫁だと思われている</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>皇女転生　～伝説の大魔導士（♂）、姫騎士となりて伝説の令嬢騎士団を作り無双する～</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GALAXIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ダメスキル【自動機能】が覚醒しました～あれ、ギルドのスカウトの皆さん、俺を「いらない」って言ってませんでした？～</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>劣等人の魔剣使い　スキルボードを駆使して最強に至る</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ハンドレッドノート－高校生探偵 天命大地－</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ともだちづくり</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>捨てられた転生賢者～魔物の森で最強の大魔帝国を作り上げる～</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ブラック国家を追放されたけど【全自動・英霊召喚】があるから何も困らない。　～最強クラスの英霊1000体が知らないうちに仕事を片付けてくれるし、みんな優しくて居心地いいんで、今さら元の国には戻りません。～</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>君が監督！</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>はじめの一歩</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>鳴るさんだぁ</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>魁の花巫女</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>私をセンターにすると誓いますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>生徒と恋はできません！</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ハプスブルク家の華麗なる受難</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>イジらないで、長瀞さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>せいぶつ部の田辺くん</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>インフェクション</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -27,6 +27,7 @@
     <sheet name="magapoke_2026-02-18" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="magapoke_2026-02-25" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="magapoke_2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="magapoke_2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13776,6 +13777,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ベイビーステップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>南海トラフ巨大地震</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GALAXIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>デッドアカウント</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -28,6 +28,7 @@
     <sheet name="magapoke_2026-02-25" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="magapoke_2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="magapoke_2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="magapoke_2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14053,6 +14054,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ベイビーステップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>デッドアカウント</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -29,6 +29,7 @@
     <sheet name="magapoke_2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="magapoke_2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="magapoke_2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="magapoke_2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14330,6 +14331,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ベイビーステップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>デッドアカウント</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -30,6 +30,7 @@
     <sheet name="magapoke_2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="magapoke_2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="magapoke_2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="magapoke_2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14607,6 +14608,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>あの島の海音荘</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -31,6 +31,7 @@
     <sheet name="magapoke_2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="magapoke_2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="magapoke_2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="magapoke_2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14884,6 +14885,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -32,6 +32,7 @@
     <sheet name="magapoke_2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="magapoke_2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="magapoke_2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="magapoke_2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15161,6 +15162,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>せいぶつ部の田辺くん</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>幼馴染とはラブコメにならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>南海トラフ巨大地震</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -33,6 +33,7 @@
     <sheet name="magapoke_2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="magapoke_2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="magapoke_2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="magapoke_2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15438,6 +15439,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>幼馴染とはラブコメにならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -34,6 +34,7 @@
     <sheet name="magapoke_2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="magapoke_2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="magapoke_2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="magapoke_2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15715,6 +15716,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南海トラフ巨大地震</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>降り積もれ孤独な死よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -35,6 +35,7 @@
     <sheet name="magapoke_2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="magapoke_2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="magapoke_2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="magapoke_2026-05-06" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15992,6 +15993,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -36,6 +36,7 @@
     <sheet name="magapoke_2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="magapoke_2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="magapoke_2026-05-06" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="magapoke_2026-05-13" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17295,6 +17296,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南海トラフ巨大地震</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -37,6 +37,7 @@
     <sheet name="magapoke_2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="magapoke_2026-05-06" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="magapoke_2026-05-13" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="magapoke_2026-05-20" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17572,6 +17573,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -38,6 +38,7 @@
     <sheet name="magapoke_2026-05-06" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="magapoke_2026-05-13" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="magapoke_2026-05-20" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="magapoke_2026-05-27" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17849,6 +17850,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>裏東京のオソロシドコロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GALAXIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -39,6 +39,7 @@
     <sheet name="magapoke_2026-05-13" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="magapoke_2026-05-20" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="magapoke_2026-05-27" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="magapoke_2026-06-03" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18126,6 +18127,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>幼馴染とはラブコメにならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>なれの果ての僕ら</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -40,6 +40,7 @@
     <sheet name="magapoke_2026-05-20" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="magapoke_2026-05-27" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="magapoke_2026-06-03" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="magapoke_2026-06-10" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18403,6 +18404,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -41,6 +41,7 @@
     <sheet name="magapoke_2026-05-27" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="magapoke_2026-06-03" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="magapoke_2026-06-10" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="magapoke_2026-06-17" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18680,6 +18681,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -42,6 +42,7 @@
     <sheet name="magapoke_2026-06-03" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="magapoke_2026-06-10" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="magapoke_2026-06-17" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="magapoke_2026-06-24" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18957,6 +18958,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>【爆アド】生まれた直後から最強悪霊と脳内バトルしてたら魔力量が測定可能域を超えてました〜悪憑の子の謙虚な覇道〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>グラぱらっ！</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -43,6 +43,7 @@
     <sheet name="magapoke_2026-06-10" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="magapoke_2026-06-17" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="magapoke_2026-06-24" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="magapoke_2026-07-01" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19234,6 +19235,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>異世界グルメで成り上がり無双～山に追放されたので、のんびりキャンプを楽しんでいたらいつの間にか強くなっていて、王侯貴族や実力者たちが俺を放っておいてくれません。一方、俺を追放した貴族たちは破滅が始まる～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -44,6 +44,7 @@
     <sheet name="magapoke_2026-06-17" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="magapoke_2026-06-24" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="magapoke_2026-07-01" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="magapoke_2026-07-08" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19511,6 +19512,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -45,6 +45,7 @@
     <sheet name="magapoke_2026-06-24" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="magapoke_2026-07-01" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="magapoke_2026-07-08" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="magapoke_2026-07-15" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19788,6 +19789,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -46,6 +46,7 @@
     <sheet name="magapoke_2026-07-01" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="magapoke_2026-07-08" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="magapoke_2026-07-15" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="magapoke_2026-07-22" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21091,6 +21092,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -47,6 +47,7 @@
     <sheet name="magapoke_2026-07-08" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="magapoke_2026-07-15" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="magapoke_2026-07-22" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="magapoke_2026-07-29" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21368,6 +21369,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>りりむホリック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -48,6 +48,7 @@
     <sheet name="magapoke_2026-07-15" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="magapoke_2026-07-22" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="magapoke_2026-07-29" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="magapoke_2026-08-05" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21645,6 +21646,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -49,6 +49,7 @@
     <sheet name="magapoke_2026-07-22" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="magapoke_2026-07-29" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="magapoke_2026-08-05" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="magapoke_2026-08-12" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21922,6 +21923,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ヒトの心が読める彼女の話</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -50,6 +50,7 @@
     <sheet name="magapoke_2026-07-29" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="magapoke_2026-08-05" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="magapoke_2026-08-12" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="magapoke_2026-08-19" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22199,6 +22200,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ヒトの心が読める彼女の話</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
